--- a/data/trans_orig/P62-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P62-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2007</t>
+          <t>Población según si percibe alguna pensión en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>491030</t>
+          <t>490935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>532390</t>
+          <t>532822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>418763</t>
+          <t>416619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>485756</t>
+          <t>482700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>917858</t>
+          <t>919681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1006017</t>
+          <t>1001885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117375</t>
+          <t>116943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158735</t>
+          <t>158830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>674964</t>
+          <t>678020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>741957</t>
+          <t>744101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804468</t>
+          <t>808600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>892627</t>
+          <t>890804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146854</t>
+          <t>150923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191524</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69065</t>
+          <t>68881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104567</t>
+          <t>105843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230433</t>
+          <t>225570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285988</t>
+          <t>284655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373341</t>
+          <t>372635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418011</t>
+          <t>413942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>896200</t>
+          <t>894924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931702</t>
+          <t>931886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279643</t>
+          <t>1280976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1335198</t>
+          <t>1340061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>49482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73345</t>
+          <t>73913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86133</t>
+          <t>85628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119271</t>
+          <t>121459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71368</t>
+          <t>70800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95592</t>
+          <t>95231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131792</t>
+          <t>131430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155444</t>
+          <t>153770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210496</t>
+          <t>208308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243634</t>
+          <t>244139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>704703</t>
+          <t>706023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>777999</t>
+          <t>776905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>538793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>619576</t>
+          <t>620420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1262052</t>
+          <t>1264825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1379693</t>
+          <t>1381379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581344</t>
+          <t>582438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>654640</t>
+          <t>653320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1726965</t>
+          <t>1726121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1811530</t>
+          <t>1807748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2326190</t>
+          <t>2324504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2443831</t>
+          <t>2441058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2012</t>
+          <t>Población según si percibe alguna pensión en 2012 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>521423</t>
+          <t>522223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>575298</t>
+          <t>574656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>505061</t>
+          <t>505027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571528</t>
+          <t>571164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043092</t>
+          <t>1043796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1131355</t>
+          <t>1135324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210297</t>
+          <t>210939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264172</t>
+          <t>263372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612935</t>
+          <t>613299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679402</t>
+          <t>679436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>838703</t>
+          <t>834734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>926966</t>
+          <t>926262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246923</t>
+          <t>245711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307067</t>
+          <t>306420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>144719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199004</t>
+          <t>197907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>407127</t>
+          <t>404749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>486607</t>
+          <t>484284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723869</t>
+          <t>724516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>784013</t>
+          <t>785225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>965257</t>
+          <t>966354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1016665</t>
+          <t>1019542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1708590</t>
+          <t>1710913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1788070</t>
+          <t>1790448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>59594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,82 +3037,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>35576</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25856</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49526</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16,05%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>81201</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>64217</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>99044</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>21,17%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35576</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24988</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>49238</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>81201</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>66756</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>100665</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>102196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127531</t>
+          <t>127719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,82 +3150,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>186129</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>172179</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>195849</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>83,95%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>77,66%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>88,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>302294</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>284451</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>319278</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>78,83%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186129</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>172467</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>196717</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>302294</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>282830</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>316739</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>829532</t>
+          <t>826521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>917731</t>
+          <t>915197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>702840</t>
+          <t>700022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>794601</t>
+          <t>792427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1541801</t>
+          <t>1551756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1682470</t>
+          <t>1691525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1060590</t>
+          <t>1063124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148789</t>
+          <t>1151800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1775827</t>
+          <t>1778001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1867588</t>
+          <t>1870406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2866280</t>
+          <t>2857225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3006949</t>
+          <t>2996994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2016</t>
+          <t>Población según si percibe alguna pensión en 2016 (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419465</t>
+          <t>418814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>461561</t>
+          <t>462837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398173</t>
+          <t>397312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>457868</t>
+          <t>460845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830582</t>
+          <t>828083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>908984</t>
+          <t>910058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146307</t>
+          <t>145031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188403</t>
+          <t>189054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452175</t>
+          <t>449198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>511870</t>
+          <t>512731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608927</t>
+          <t>607853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>687329</t>
+          <t>689828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>355482</t>
+          <t>354867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421168</t>
+          <t>421760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226296</t>
+          <t>230826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289897</t>
+          <t>292103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>604921</t>
+          <t>604332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>693269</t>
+          <t>693357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710927</t>
+          <t>710335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>776613</t>
+          <t>777228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013601</t>
+          <t>1011395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1077202</t>
+          <t>1072672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1742323</t>
+          <t>1742235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1830671</t>
+          <t>1831260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39388</t>
+          <t>40640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68130</t>
+          <t>67157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102101</t>
+          <t>103493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143683</t>
+          <t>142735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108361</t>
+          <t>109202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136001</t>
+          <t>137179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169100</t>
+          <t>170073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197842</t>
+          <t>196590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286567</t>
+          <t>287515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328149</t>
+          <t>326757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>853779</t>
+          <t>854515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>941046</t>
+          <t>945374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>692959</t>
+          <t>694886</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>790172</t>
+          <t>789375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1567843</t>
+          <t>1574572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1700884</t>
+          <t>1707814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>991937</t>
+          <t>987609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1079204</t>
+          <t>1078468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1660599</t>
+          <t>1661396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1757812</t>
+          <t>1755885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2682869</t>
+          <t>2675939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2815910</t>
+          <t>2809181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe alguna pensión en 2023</t>
+          <t>Población según si percibe alguna pensión en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282881</t>
+          <t>282366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312071</t>
+          <t>312502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361068</t>
+          <t>359902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>398809</t>
+          <t>396364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>650372</t>
+          <t>650652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>698984</t>
+          <t>702236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69669</t>
+          <t>69238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98859</t>
+          <t>99374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270528</t>
+          <t>272973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308269</t>
+          <t>309435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352093</t>
+          <t>348841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>400705</t>
+          <t>400425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>355925</t>
+          <t>357495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>426274</t>
+          <t>430005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328186</t>
+          <t>327835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>791371</t>
+          <t>803389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729528</t>
+          <t>728001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1225830</t>
+          <t>1259746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476426</t>
+          <t>472695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>546775</t>
+          <t>545205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494523</t>
+          <t>482505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>957708</t>
+          <t>958059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>962764</t>
+          <t>928848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1459066</t>
+          <t>1460593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94490</t>
+          <t>95160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124175</t>
+          <t>122050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>63090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86099</t>
+          <t>85874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164083</t>
+          <t>165554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200824</t>
+          <t>200090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69221</t>
+          <t>71346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98906</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130515</t>
+          <t>130740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153468</t>
+          <t>153524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209186</t>
+          <t>209920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245927</t>
+          <t>244456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>753042</t>
+          <t>755077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>842535</t>
+          <t>843575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>804830</t>
+          <t>800311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1259545</t>
+          <t>1275030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1607452</t>
+          <t>1602702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2048576</t>
+          <t>2096065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635300</t>
+          <t>634260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>724793</t>
+          <t>722758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>912300</t>
+          <t>896815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1367015</t>
+          <t>1371534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1601105</t>
+          <t>1553616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2042229</t>
+          <t>2046979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P62-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>490935</t>
+          <t>490287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>532822</t>
+          <t>530610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>416619</t>
+          <t>419289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>482700</t>
+          <t>483733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>919681</t>
+          <t>918187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1001885</t>
+          <t>1001650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>119155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158830</t>
+          <t>159478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>678020</t>
+          <t>676987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>744101</t>
+          <t>741431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808600</t>
+          <t>808835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890804</t>
+          <t>892298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150923</t>
+          <t>148913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192230</t>
+          <t>192822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68881</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105843</t>
+          <t>107380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225570</t>
+          <t>227301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284655</t>
+          <t>288736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372635</t>
+          <t>372043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413942</t>
+          <t>415952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894924</t>
+          <t>893387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931886</t>
+          <t>930711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1280976</t>
+          <t>1276895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1340061</t>
+          <t>1338330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>48792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73913</t>
+          <t>72708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>53894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85628</t>
+          <t>85615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>119260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95231</t>
+          <t>95921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131430</t>
+          <t>131160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153770</t>
+          <t>153985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208308</t>
+          <t>210507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244139</t>
+          <t>244152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>704978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>776905</t>
+          <t>776480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>538793</t>
+          <t>536304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>620420</t>
+          <t>621544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1264825</t>
+          <t>1267016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1381379</t>
+          <t>1382544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>582438</t>
+          <t>582863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>653320</t>
+          <t>654365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1726121</t>
+          <t>1724997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1807748</t>
+          <t>1810237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2324504</t>
+          <t>2323339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2441058</t>
+          <t>2438867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>522223</t>
+          <t>522784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>574656</t>
+          <t>576834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>505027</t>
+          <t>504414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571164</t>
+          <t>572080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1043796</t>
+          <t>1045123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1135324</t>
+          <t>1132304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210939</t>
+          <t>208761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263372</t>
+          <t>262811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613299</t>
+          <t>612383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679436</t>
+          <t>680049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>834734</t>
+          <t>837754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>926262</t>
+          <t>924935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245711</t>
+          <t>246187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306420</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144719</t>
+          <t>147497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197907</t>
+          <t>198460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404749</t>
+          <t>408039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484284</t>
+          <t>493081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724516</t>
+          <t>726911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>785225</t>
+          <t>784749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>966354</t>
+          <t>965801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019542</t>
+          <t>1016764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1710913</t>
+          <t>1702116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1790448</t>
+          <t>1787158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59594</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49526</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64217</t>
+          <t>64973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>100368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102196</t>
+          <t>103444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127719</t>
+          <t>129359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172179</t>
+          <t>172795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195849</t>
+          <t>196185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284451</t>
+          <t>283127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319278</t>
+          <t>318522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>826521</t>
+          <t>827165</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>915197</t>
+          <t>913772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>700022</t>
+          <t>700994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>792427</t>
+          <t>791078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1551756</t>
+          <t>1546579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1691525</t>
+          <t>1678586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1063124</t>
+          <t>1064549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1151800</t>
+          <t>1151156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1778001</t>
+          <t>1779350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1870406</t>
+          <t>1869434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2857225</t>
+          <t>2870164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2996994</t>
+          <t>3002171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>418814</t>
+          <t>417820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>462837</t>
+          <t>462418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397312</t>
+          <t>394343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460845</t>
+          <t>459563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>828083</t>
+          <t>829902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>910058</t>
+          <t>904334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145031</t>
+          <t>145450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189054</t>
+          <t>190048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449198</t>
+          <t>450480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512731</t>
+          <t>515700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>607853</t>
+          <t>613577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689828</t>
+          <t>688009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354867</t>
+          <t>355496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421760</t>
+          <t>419388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230826</t>
+          <t>226871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>292103</t>
+          <t>287288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>604332</t>
+          <t>609231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>693357</t>
+          <t>698061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>710335</t>
+          <t>712707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>777228</t>
+          <t>776599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1011395</t>
+          <t>1016210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1072672</t>
+          <t>1076627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1742235</t>
+          <t>1737531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1831260</t>
+          <t>1826361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55841</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83818</t>
+          <t>83670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67157</t>
+          <t>68310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103493</t>
+          <t>103737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142735</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109202</t>
+          <t>109350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137179</t>
+          <t>137576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170073</t>
+          <t>168920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196590</t>
+          <t>197792</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287515</t>
+          <t>287279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326757</t>
+          <t>326513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>854515</t>
+          <t>851113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>945374</t>
+          <t>942934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>694886</t>
+          <t>694199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>789375</t>
+          <t>789939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1574572</t>
+          <t>1575918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1707814</t>
+          <t>1701106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>987609</t>
+          <t>990049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1078468</t>
+          <t>1081870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1661396</t>
+          <t>1660832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1755885</t>
+          <t>1756572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2675939</t>
+          <t>2682647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2809181</t>
+          <t>2807835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>298869</t>
+          <t>320791</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282366</t>
+          <t>302573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312502</t>
+          <t>333767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>378251</t>
+          <t>411773</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>359902</t>
+          <t>392100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>396364</t>
+          <t>433491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>677120</t>
+          <t>732564</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>650652</t>
+          <t>703973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>758906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82871</t>
+          <t>92605</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69238</t>
+          <t>79629</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>110823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291086</t>
+          <t>317520</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272973</t>
+          <t>295802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309435</t>
+          <t>337193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>373957</t>
+          <t>410126</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348841</t>
+          <t>383784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>400425</t>
+          <t>438717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>381740</t>
+          <t>413396</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>381740</t>
+          <t>413396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>381740</t>
+          <t>413396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>669337</t>
+          <t>729293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>669337</t>
+          <t>729293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>669337</t>
+          <t>729293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1051077</t>
+          <t>1142690</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1051077</t>
+          <t>1142690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1051077</t>
+          <t>1142690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>392185</t>
+          <t>427767</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357495</t>
+          <t>394666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>430005</t>
+          <t>462250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>488387</t>
+          <t>310825</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327835</t>
+          <t>283354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>803389</t>
+          <t>337744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>880573</t>
+          <t>738592</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>728001</t>
+          <t>696531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1259746</t>
+          <t>781515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>510515</t>
+          <t>523979</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472695</t>
+          <t>489496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>545205</t>
+          <t>557080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>797507</t>
+          <t>907736</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>880817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>958059</t>
+          <t>935207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1308021</t>
+          <t>1431715</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>928848</t>
+          <t>1388792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1460593</t>
+          <t>1473776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>902700</t>
+          <t>951746</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>902700</t>
+          <t>951746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>902700</t>
+          <t>951746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1285894</t>
+          <t>1218561</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1285894</t>
+          <t>1218561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1285894</t>
+          <t>1218561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2188594</t>
+          <t>2170307</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2188594</t>
+          <t>2170307</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2188594</t>
+          <t>2170307</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108345</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95160</t>
+          <t>105396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122050</t>
+          <t>137765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73973</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>73413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85874</t>
+          <t>99310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>182318</t>
+          <t>208644</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165554</t>
+          <t>188602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200090</t>
+          <t>228567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85051</t>
+          <t>94202</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>79407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98236</t>
+          <t>111776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142641</t>
+          <t>162253</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130740</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153524</t>
+          <t>174514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>227692</t>
+          <t>256455</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209920</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244456</t>
+          <t>276497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>193396</t>
+          <t>217172</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>193396</t>
+          <t>217172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>193396</t>
+          <t>217172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>216614</t>
+          <t>247927</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216614</t>
+          <t>247927</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>216614</t>
+          <t>247927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>410010</t>
+          <t>465099</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>410010</t>
+          <t>465099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>410010</t>
+          <t>465099</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>799398</t>
+          <t>871527</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>755077</t>
+          <t>828989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>843575</t>
+          <t>916455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>940611</t>
+          <t>808272</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>800311</t>
+          <t>767574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1275030</t>
+          <t>846083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1740010</t>
+          <t>1679800</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1602702</t>
+          <t>1624681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2096065</t>
+          <t>1732932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>678437</t>
+          <t>710787</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634260</t>
+          <t>665859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>722758</t>
+          <t>753325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1231234</t>
+          <t>1387509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>896815</t>
+          <t>1349698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1371534</t>
+          <t>1428207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1909671</t>
+          <t>2098296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1553616</t>
+          <t>2045164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2046979</t>
+          <t>2153415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1477835</t>
+          <t>1582314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1477835</t>
+          <t>1582314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1477835</t>
+          <t>1582314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2171845</t>
+          <t>2195781</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2171845</t>
+          <t>2195781</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2171845</t>
+          <t>2195781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3649681</t>
+          <t>3778096</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3649681</t>
+          <t>3778096</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3649681</t>
+          <t>3778096</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
